--- a/data.mn/public/datasets/household-expenditure-by-location.xlsx
+++ b/data.mn/public/datasets/household-expenditure-by-location.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,8 +413,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -506,6 +538,9 @@
       <c r="AC1" t="n">
         <v>2024</v>
       </c>
+      <c r="AD1" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -595,7 +630,10 @@
         <v>2196615</v>
       </c>
       <c r="AC2" t="n">
-        <v>2631689</v>
+        <v>2638159</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3141317</v>
       </c>
     </row>
     <row r="3">
@@ -686,7 +724,10 @@
         <v>2314620</v>
       </c>
       <c r="AC3" t="n">
-        <v>2818937</v>
+        <v>2824079</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3326146</v>
       </c>
     </row>
     <row r="4">
@@ -777,7 +818,10 @@
         <v>1933596</v>
       </c>
       <c r="AC4" t="n">
-        <v>2235728</v>
+        <v>2245940</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2737181</v>
       </c>
     </row>
   </sheetData>
